--- a/app/reports/JCAP_research.xlsx
+++ b/app/reports/JCAP_research.xlsx
@@ -618,7 +618,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-05-30 22:16 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-05-31 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
